--- a/administrative_forms/018_government_assistance_records_release_form--administrative_forms.xlsx
+++ b/administrative_forms/018_government_assistance_records_release_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Title 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Organization's Contact Person's Email</t>
+          <t>Form Title 13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Form Title 22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Form Title 23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'administrative_forms'}</t>
+          <t>administrative_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Administrative Forms'}</t>
+          <t>Administrative Forms</t>
         </is>
       </c>
     </row>
@@ -1148,165 +1148,165 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'renewal'}</t>
+          <t>renewal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Renewal'}</t>
+          <t>Renewal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'general_assistance'}</t>
+          <t>general_assistance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'General Assistance'}</t>
+          <t>General Assistance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'department_of_education'}</t>
+          <t>department_of_education</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Department of Education'}</t>
+          <t>Department of Education</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'department_of_health_and_human_services'}</t>
+          <t>department_of_health_and_human_services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Department of Health and Human Services'}</t>
+          <t>Department of Health and Human Services</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_14_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>form_title_14_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
